--- a/backtest_runs/20260410_193731/by_symbol/PICT/PICT.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/PICT/PICT.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>100284.72</v>
@@ -909,7 +909,7 @@
         <v>-1174.469999999994</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>106050.3</v>
@@ -1185,7 +1185,7 @@
         <v>-3559</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>119716.86</v>
@@ -1277,7 +1277,7 @@
         <v>-2313.349999999995</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>119788.04</v>
@@ -1323,7 +1323,7 @@
         <v>-1138.880000000001</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>118649.16</v>
@@ -1415,7 +1415,7 @@
         <v>-747.3900000000031</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>121638.72</v>
@@ -1461,7 +1461,7 @@
         <v>-1494.780000000006</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>120143.94</v>
@@ -1645,7 +1645,7 @@
         <v>-320.3099999999995</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>123987.66</v>
